--- a/data/trans_orig/POLIPATOLOGIA_Lim_5-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_Lim_5-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante en 2012</t>
+          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5633</t>
+          <t>6272</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20437</t>
+          <t>20376</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15235</t>
+          <t>15073</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35804</t>
+          <t>36262</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25325</t>
+          <t>25069</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50280</t>
+          <t>49238</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>274301</t>
+          <t>274362</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>289105</t>
+          <t>288466</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>251441</t>
+          <t>250983</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>272010</t>
+          <t>272172</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>531703</t>
+          <t>532745</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>556658</t>
+          <t>556914</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15647</t>
+          <t>15747</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38510</t>
+          <t>37162</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34566</t>
+          <t>35339</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62574</t>
+          <t>62428</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56446</t>
+          <t>57513</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91739</t>
+          <t>91953</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>467017</t>
+          <t>468365</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>489880</t>
+          <t>489780</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>461191</t>
+          <t>461337</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>489199</t>
+          <t>488426</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>937553</t>
+          <t>937339</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>972846</t>
+          <t>971779</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19186</t>
+          <t>17947</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18320</t>
+          <t>18527</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39976</t>
+          <t>39834</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26171</t>
+          <t>25651</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50973</t>
+          <t>49782</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>304860</t>
+          <t>306099</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>320031</t>
+          <t>320011</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>301044</t>
+          <t>301186</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>322700</t>
+          <t>322493</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>614093</t>
+          <t>615284</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>638895</t>
+          <t>639415</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8477</t>
+          <t>8839</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24102</t>
+          <t>24773</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40883</t>
+          <t>40430</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68985</t>
+          <t>66668</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51967</t>
+          <t>52275</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83702</t>
+          <t>85681</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>349880</t>
+          <t>349209</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>365505</t>
+          <t>365143</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>319966</t>
+          <t>322283</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>348068</t>
+          <t>348521</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>679231</t>
+          <t>677252</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>710966</t>
+          <t>710658</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,15%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10754</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26961</t>
+          <t>27216</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28052</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51689</t>
+          <t>51741</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41247</t>
+          <t>43498</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72952</t>
+          <t>74291</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>185657</t>
+          <t>185402</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>202617</t>
+          <t>201864</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>167902</t>
+          <t>167850</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>191539</t>
+          <t>192323</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>359257</t>
+          <t>357918</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>390962</t>
+          <t>388711</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>89,94%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21131</t>
+          <t>22933</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10454</t>
+          <t>10493</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27454</t>
+          <t>27633</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21309</t>
+          <t>21472</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>43378</t>
+          <t>43025</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252850</t>
+          <t>251048</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266751</t>
+          <t>265872</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>252577</t>
+          <t>252398</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>269577</t>
+          <t>269538</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>510634</t>
+          <t>510987</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>532703</t>
+          <t>532540</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,12%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10123</t>
+          <t>10170</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26050</t>
+          <t>26102</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47646</t>
+          <t>49144</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80569</t>
+          <t>79637</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62976</t>
+          <t>62895</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>99868</t>
+          <t>99353</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>636738</t>
+          <t>636686</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>652665</t>
+          <t>652618</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>613284</t>
+          <t>614216</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>646207</t>
+          <t>644709</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1256773</t>
+          <t>1257288</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1293665</t>
+          <t>1293746</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7340</t>
+          <t>7437</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21253</t>
+          <t>21723</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>45684</t>
+          <t>46901</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>77242</t>
+          <t>76948</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>57255</t>
+          <t>58532</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>91876</t>
+          <t>91617</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>757845</t>
+          <t>757375</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>771758</t>
+          <t>771661</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>746611</t>
+          <t>746905</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>778169</t>
+          <t>776952</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1511075</t>
+          <t>1511334</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1545696</t>
+          <t>1544419</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>99877</t>
+          <t>99908</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>145479</t>
+          <t>147553</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>293090</t>
+          <t>296365</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>366377</t>
+          <t>365898</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>409542</t>
+          <t>410937</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>495356</t>
+          <t>492949</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3281300</t>
+          <t>3279226</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3326902</t>
+          <t>3326871</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3191932</t>
+          <t>3192411</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3265219</t>
+          <t>3261944</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6489732</t>
+          <t>6492139</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6575546</t>
+          <t>6574151</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3860,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante en 2016</t>
+          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>5849</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>20386</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27826</t>
+          <t>27110</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51868</t>
+          <t>50755</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37702</t>
+          <t>36024</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66711</t>
+          <t>65028</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>274761</t>
+          <t>273375</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288233</t>
+          <t>287912</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>236835</t>
+          <t>237948</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>260877</t>
+          <t>261593</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>515753</t>
+          <t>517436</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>544762</t>
+          <t>546440</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,82%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10530</t>
+          <t>10687</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19330</t>
+          <t>19340</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42193</t>
+          <t>41214</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22611</t>
+          <t>22650</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48254</t>
+          <t>47508</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>492045</t>
+          <t>491888</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500838</t>
+          <t>500846</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>480891</t>
+          <t>481870</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>503754</t>
+          <t>503744</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>977405</t>
+          <t>978151</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1003048</t>
+          <t>1003009</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10996</t>
+          <t>10477</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10087</t>
+          <t>10118</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29250</t>
+          <t>28990</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14034</t>
+          <t>13655</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>33643</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>307569</t>
+          <t>308088</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316210</t>
+          <t>316888</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>307059</t>
+          <t>307319</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>326222</t>
+          <t>326191</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>620407</t>
+          <t>621231</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>640840</t>
+          <t>641219</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10486</t>
+          <t>10393</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27728</t>
+          <t>27250</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36155</t>
+          <t>36798</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63309</t>
+          <t>63693</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50452</t>
+          <t>50615</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84663</t>
+          <t>83952</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>342236</t>
+          <t>342714</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>359478</t>
+          <t>359571</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>323974</t>
+          <t>323590</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>351128</t>
+          <t>350485</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>672584</t>
+          <t>673295</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>706795</t>
+          <t>706632</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,32%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17122</t>
+          <t>17313</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14113</t>
+          <t>14593</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31381</t>
+          <t>33534</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21881</t>
+          <t>21638</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42048</t>
+          <t>44096</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>194099</t>
+          <t>193908</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>206487</t>
+          <t>206341</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>187206</t>
+          <t>185053</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>204474</t>
+          <t>203994</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>387760</t>
+          <t>385712</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>407927</t>
+          <t>408170</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,97%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>3033</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13168</t>
+          <t>12612</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11198</t>
+          <t>11121</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28128</t>
+          <t>28757</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>15625</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36130</t>
+          <t>36614</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249955</t>
+          <t>250511</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>259967</t>
+          <t>260090</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>244987</t>
+          <t>244358</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>261917</t>
+          <t>261994</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>500108</t>
+          <t>499624</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>520173</t>
+          <t>520613</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,09%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17015</t>
+          <t>17654</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38494</t>
+          <t>39735</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48084</t>
+          <t>48292</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>78102</t>
+          <t>80229</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>72105</t>
+          <t>71153</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>110744</t>
+          <t>110183</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>618064</t>
+          <t>616823</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>639543</t>
+          <t>638904</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>613192</t>
+          <t>611065</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>643210</t>
+          <t>643002</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1237108</t>
+          <t>1237669</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1275747</t>
+          <t>1276699</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,72%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16004</t>
+          <t>16371</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36039</t>
+          <t>35800</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>65809</t>
+          <t>65556</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>103014</t>
+          <t>103380</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>88054</t>
+          <t>87616</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>133325</t>
+          <t>130983</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>742544</t>
+          <t>742783</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>762579</t>
+          <t>762212</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>723153</t>
+          <t>722787</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>760358</t>
+          <t>760611</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1471425</t>
+          <t>1473767</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1516696</t>
+          <t>1517134</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,54%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>85975</t>
+          <t>87899</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>127247</t>
+          <t>127715</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>281573</t>
+          <t>284649</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>356245</t>
+          <t>358179</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>380773</t>
+          <t>382863</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>462015</t>
+          <t>464351</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3267103</t>
+          <t>3266635</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3308375</t>
+          <t>3306451</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3188297</t>
+          <t>3186363</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3262969</t>
+          <t>3259893</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6476877</t>
+          <t>6474541</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6558119</t>
+          <t>6556029</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,48%</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante en 2023</t>
+          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>3996</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14389</t>
+          <t>14304</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11859</t>
+          <t>11604</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23139</t>
+          <t>22668</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17499</t>
+          <t>17910</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32656</t>
+          <t>32814</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>297054</t>
+          <t>297139</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>307517</t>
+          <t>307447</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>266496</t>
+          <t>266967</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>277776</t>
+          <t>278031</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>568421</t>
+          <t>568263</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>583578</t>
+          <t>583167</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16947</t>
+          <t>16533</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38345</t>
+          <t>38548</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56703</t>
+          <t>56717</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80713</t>
+          <t>82411</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>78423</t>
+          <t>79573</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>112880</t>
+          <t>112638</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>480045</t>
+          <t>479842</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>501443</t>
+          <t>501857</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>434256</t>
+          <t>432558</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>458266</t>
+          <t>458252</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>920479</t>
+          <t>920721</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>954936</t>
+          <t>953786</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,3%</t>
         </is>
       </c>
     </row>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26005</t>
+          <t>26009</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45118</t>
+          <t>45250</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46148</t>
+          <t>45699</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66874</t>
+          <t>66916</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>78470</t>
+          <t>77527</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104933</t>
+          <t>106816</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>270932</t>
+          <t>270800</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>290045</t>
+          <t>290041</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>282254</t>
+          <t>282212</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>302980</t>
+          <t>303429</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>560245</t>
+          <t>558362</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>586708</t>
+          <t>587651</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,34%</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20554</t>
+          <t>20860</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41776</t>
+          <t>40790</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34138</t>
+          <t>34223</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75201</t>
+          <t>75557</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>64553</t>
+          <t>63380</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>106804</t>
+          <t>106713</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>270781</t>
+          <t>271767</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>292003</t>
+          <t>291697</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>400517</t>
+          <t>400161</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>441580</t>
+          <t>441495</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>681470</t>
+          <t>681561</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>723721</t>
+          <t>724894</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,96%</t>
         </is>
       </c>
     </row>
@@ -8750,12 +8750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6873</t>
+          <t>6392</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16073</t>
+          <t>15611</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8785,12 +8785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14818</t>
+          <t>15966</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39015</t>
+          <t>39597</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8800,12 +8800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26773</t>
+          <t>27883</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50034</t>
+          <t>50579</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>162669</t>
+          <t>163131</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>171869</t>
+          <t>172350</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>219764</t>
+          <t>219182</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>243961</t>
+          <t>242813</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>387487</t>
+          <t>386942</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>410748</t>
+          <t>409638</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32053</t>
+          <t>32633</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49653</t>
+          <t>50128</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55588</t>
+          <t>55377</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>75572</t>
+          <t>75629</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>92180</t>
+          <t>91954</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>118576</t>
+          <t>118691</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>219983</t>
+          <t>219508</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237583</t>
+          <t>237003</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>181484</t>
+          <t>181427</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>201468</t>
+          <t>201679</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>408116</t>
+          <t>408001</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>434512</t>
+          <t>434738</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,54%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38644</t>
+          <t>39585</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>65508</t>
+          <t>67517</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>69655</t>
+          <t>65203</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>184727</t>
+          <t>186144</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>120042</t>
+          <t>118851</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>226072</t>
+          <t>227943</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>558771</t>
+          <t>556762</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>585635</t>
+          <t>584694</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>664538</t>
+          <t>663121</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>779610</t>
+          <t>784062</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1247472</t>
+          <t>1245601</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1353502</t>
+          <t>1354693</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,93%</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12571</t>
+          <t>12314</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45622</t>
+          <t>45704</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>76102</t>
+          <t>74287</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>108592</t>
+          <t>105351</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>74192</t>
+          <t>76658</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>147844</t>
+          <t>150280</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>883098</t>
+          <t>883016</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>916149</t>
+          <t>916406</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>609139</t>
+          <t>612380</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>641629</t>
+          <t>643444</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1498608</t>
+          <t>1496172</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1572260</t>
+          <t>1569794</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>178594</t>
+          <t>178838</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>261829</t>
+          <t>263678</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>417804</t>
+          <t>413012</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>567954</t>
+          <t>567137</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>652587</t>
+          <t>650438</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>812477</t>
+          <t>818617</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3197988</t>
+          <t>3196139</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3281223</t>
+          <t>3280979</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3144326</t>
+          <t>3145143</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3294476</t>
+          <t>3299268</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6359620</t>
+          <t>6353480</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6519510</t>
+          <t>6521659</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,93%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/POLIPATOLOGIA_Lim_5-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_Lim_5-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6272</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20376</t>
+          <t>20255</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15073</t>
+          <t>14978</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36262</t>
+          <t>36198</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25069</t>
+          <t>24844</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49238</t>
+          <t>48777</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>274362</t>
+          <t>274483</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288466</t>
+          <t>288962</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>250983</t>
+          <t>251047</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>272172</t>
+          <t>272267</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>532745</t>
+          <t>533206</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>556914</t>
+          <t>557139</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,73%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15747</t>
+          <t>15647</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37162</t>
+          <t>38322</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35339</t>
+          <t>34431</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62428</t>
+          <t>61905</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57513</t>
+          <t>57496</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91953</t>
+          <t>92236</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>468365</t>
+          <t>467205</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>489780</t>
+          <t>489880</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>461337</t>
+          <t>461860</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>488426</t>
+          <t>489334</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>937339</t>
+          <t>937056</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>971779</t>
+          <t>971796</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4035</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17947</t>
+          <t>17027</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18527</t>
+          <t>18061</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39834</t>
+          <t>39421</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25651</t>
+          <t>26184</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49782</t>
+          <t>51252</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>306099</t>
+          <t>307019</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>320011</t>
+          <t>320014</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>301186</t>
+          <t>301599</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>322493</t>
+          <t>322959</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>615284</t>
+          <t>613814</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>639415</t>
+          <t>638882</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8839</t>
+          <t>8918</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24773</t>
+          <t>24555</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40430</t>
+          <t>39517</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66668</t>
+          <t>66477</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52275</t>
+          <t>53220</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85681</t>
+          <t>84023</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>349209</t>
+          <t>349427</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>365143</t>
+          <t>365064</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>322283</t>
+          <t>322474</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>348521</t>
+          <t>349434</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>677252</t>
+          <t>678910</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>710658</t>
+          <t>709713</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,02%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>10217</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27216</t>
+          <t>26699</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>28777</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51741</t>
+          <t>51393</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43498</t>
+          <t>43209</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74291</t>
+          <t>70298</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>185402</t>
+          <t>185919</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>201864</t>
+          <t>202401</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>167850</t>
+          <t>168198</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>192323</t>
+          <t>190814</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>357918</t>
+          <t>361911</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>388711</t>
+          <t>389000</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,0%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>7223</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22933</t>
+          <t>21768</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10493</t>
+          <t>11324</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27633</t>
+          <t>27113</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21472</t>
+          <t>20839</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>43025</t>
+          <t>44675</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>251048</t>
+          <t>252213</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265872</t>
+          <t>266758</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>252398</t>
+          <t>252918</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>269538</t>
+          <t>268707</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>510987</t>
+          <t>509337</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>532540</t>
+          <t>533173</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,24%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10170</t>
+          <t>10221</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26102</t>
+          <t>28415</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49144</t>
+          <t>48260</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>79637</t>
+          <t>78438</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62895</t>
+          <t>63237</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>99353</t>
+          <t>101825</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>636686</t>
+          <t>634373</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>652618</t>
+          <t>652567</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>614216</t>
+          <t>615415</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>644709</t>
+          <t>645593</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1257288</t>
+          <t>1254816</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1293746</t>
+          <t>1293404</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7437</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21723</t>
+          <t>22433</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>46901</t>
+          <t>44591</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>76948</t>
+          <t>76561</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>58532</t>
+          <t>57564</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>91617</t>
+          <t>90759</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>757375</t>
+          <t>756665</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>771661</t>
+          <t>772588</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>746905</t>
+          <t>747292</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>776952</t>
+          <t>779262</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1511334</t>
+          <t>1512192</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1544419</t>
+          <t>1545387</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>99908</t>
+          <t>101165</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>147553</t>
+          <t>149257</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>296365</t>
+          <t>297365</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>365898</t>
+          <t>371449</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>410937</t>
+          <t>412347</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>492949</t>
+          <t>497420</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3279226</t>
+          <t>3277522</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3326871</t>
+          <t>3325614</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3192411</t>
+          <t>3186860</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3261944</t>
+          <t>3260944</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6492139</t>
+          <t>6487668</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6574151</t>
+          <t>6572741</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5849</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20386</t>
+          <t>19644</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27110</t>
+          <t>26453</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50755</t>
+          <t>51624</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36024</t>
+          <t>36261</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65028</t>
+          <t>64497</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>273375</t>
+          <t>274117</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>287912</t>
+          <t>287768</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>237948</t>
+          <t>237079</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>261593</t>
+          <t>262250</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>517436</t>
+          <t>517967</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>546440</t>
+          <t>546203</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,77%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1732</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10687</t>
+          <t>10834</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19340</t>
+          <t>18032</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41214</t>
+          <t>40542</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22650</t>
+          <t>22246</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47508</t>
+          <t>45549</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>491888</t>
+          <t>491741</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500846</t>
+          <t>500843</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>481870</t>
+          <t>482542</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>503744</t>
+          <t>505052</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>978151</t>
+          <t>980110</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1003009</t>
+          <t>1003413</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>1730</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10477</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10118</t>
+          <t>10596</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28990</t>
+          <t>30508</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13655</t>
+          <t>14414</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33643</t>
+          <t>34276</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308088</t>
+          <t>308455</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316888</t>
+          <t>316835</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>307319</t>
+          <t>305801</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>326191</t>
+          <t>325713</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>621231</t>
+          <t>620598</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>641219</t>
+          <t>640460</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10393</t>
+          <t>10849</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27250</t>
+          <t>26928</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36798</t>
+          <t>35771</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63693</t>
+          <t>64292</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50615</t>
+          <t>52978</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83952</t>
+          <t>84243</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>342714</t>
+          <t>343036</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>359571</t>
+          <t>359115</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>323590</t>
+          <t>322991</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>350485</t>
+          <t>351512</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>673295</t>
+          <t>673004</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>706632</t>
+          <t>704269</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,0%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>4854</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17313</t>
+          <t>16910</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14593</t>
+          <t>14301</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33534</t>
+          <t>32808</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21638</t>
+          <t>21696</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44096</t>
+          <t>42587</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>193908</t>
+          <t>194311</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>206341</t>
+          <t>206367</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>185053</t>
+          <t>185779</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203994</t>
+          <t>204286</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>385712</t>
+          <t>387221</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>408170</t>
+          <t>408112</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,95%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>3169</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12612</t>
+          <t>13943</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11121</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28757</t>
+          <t>28011</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15625</t>
+          <t>16675</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36614</t>
+          <t>35956</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>250511</t>
+          <t>249180</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260090</t>
+          <t>259954</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>244358</t>
+          <t>245104</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>261994</t>
+          <t>262796</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>499624</t>
+          <t>500282</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>520613</t>
+          <t>519563</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17654</t>
+          <t>17387</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39735</t>
+          <t>37735</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48292</t>
+          <t>49460</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80229</t>
+          <t>80050</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>71153</t>
+          <t>73202</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>110183</t>
+          <t>110631</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>616823</t>
+          <t>618823</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>638904</t>
+          <t>639171</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>611065</t>
+          <t>611244</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>643002</t>
+          <t>641834</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1237669</t>
+          <t>1237221</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1276699</t>
+          <t>1274650</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,57%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16371</t>
+          <t>15916</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>35800</t>
+          <t>37219</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>65556</t>
+          <t>65984</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>103380</t>
+          <t>102162</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>87616</t>
+          <t>87716</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>130983</t>
+          <t>129432</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>742783</t>
+          <t>741364</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>762212</t>
+          <t>762667</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>722787</t>
+          <t>724005</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>760611</t>
+          <t>760183</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1473767</t>
+          <t>1475318</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1517134</t>
+          <t>1517034</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,53%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>87899</t>
+          <t>85097</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>127715</t>
+          <t>129311</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>284649</t>
+          <t>281670</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>358179</t>
+          <t>355091</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>382863</t>
+          <t>383156</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>464351</t>
+          <t>466397</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3266635</t>
+          <t>3265039</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3306451</t>
+          <t>3309253</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3186363</t>
+          <t>3189451</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3259893</t>
+          <t>3262872</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6474541</t>
+          <t>6472495</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6556029</t>
+          <t>6555736</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7373,32 +7373,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7592</t>
+          <t>7931</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3996</t>
+          <t>3873</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14304</t>
+          <t>14505</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7408,32 +7408,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16774</t>
+          <t>18484</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11604</t>
+          <t>13284</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22668</t>
+          <t>24659</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7443,32 +7443,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>24366</t>
+          <t>26415</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17910</t>
+          <t>19245</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32814</t>
+          <t>35043</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -7486,32 +7486,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>303851</t>
+          <t>310914</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>297139</t>
+          <t>304340</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>307447</t>
+          <t>314972</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7521,32 +7521,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>272861</t>
+          <t>297577</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>266967</t>
+          <t>291402</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>278031</t>
+          <t>302777</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7556,32 +7556,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>576711</t>
+          <t>608491</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>568263</t>
+          <t>599863</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>583167</t>
+          <t>615661</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,97%</t>
         </is>
       </c>
     </row>
@@ -7599,17 +7599,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7634,17 +7634,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7669,17 +7669,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7716,32 +7716,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26343</t>
+          <t>28174</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16533</t>
+          <t>18673</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38548</t>
+          <t>41432</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7751,32 +7751,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>67767</t>
+          <t>70617</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56717</t>
+          <t>58391</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82411</t>
+          <t>85114</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7786,32 +7786,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>94110</t>
+          <t>98791</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79573</t>
+          <t>80979</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>112638</t>
+          <t>117112</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -7829,32 +7829,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>492047</t>
+          <t>502473</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>479842</t>
+          <t>489215</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>501857</t>
+          <t>511974</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7864,32 +7864,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>447202</t>
+          <t>475877</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>432558</t>
+          <t>461380</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>458252</t>
+          <t>488103</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7899,32 +7899,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>939249</t>
+          <t>978350</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>920721</t>
+          <t>960029</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>953786</t>
+          <t>996162</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,48%</t>
         </is>
       </c>
     </row>
@@ -7942,17 +7942,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7977,17 +7977,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8012,17 +8012,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8059,32 +8059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>34542</t>
+          <t>34187</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26009</t>
+          <t>25958</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45250</t>
+          <t>44578</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8094,32 +8094,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>55881</t>
+          <t>56545</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45699</t>
+          <t>46596</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66916</t>
+          <t>68516</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8129,32 +8129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>90422</t>
+          <t>90733</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>77527</t>
+          <t>77554</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>106816</t>
+          <t>104839</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,59%</t>
         </is>
       </c>
     </row>
@@ -8172,32 +8172,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>281508</t>
+          <t>281806</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>270800</t>
+          <t>271415</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>290041</t>
+          <t>290035</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8207,32 +8207,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>293247</t>
+          <t>299836</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>282212</t>
+          <t>287865</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>303429</t>
+          <t>309785</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8242,32 +8242,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>574756</t>
+          <t>581642</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>558362</t>
+          <t>567536</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>587651</t>
+          <t>594821</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,47%</t>
         </is>
       </c>
     </row>
@@ -8285,17 +8285,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8355,17 +8355,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8402,32 +8402,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29905</t>
+          <t>32397</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20860</t>
+          <t>23162</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40790</t>
+          <t>45336</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8437,32 +8437,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>58078</t>
+          <t>62063</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34223</t>
+          <t>52624</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75557</t>
+          <t>74565</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8472,32 +8472,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>87983</t>
+          <t>94460</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63380</t>
+          <t>79821</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>106713</t>
+          <t>109994</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -8515,32 +8515,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>282652</t>
+          <t>340748</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>271767</t>
+          <t>327809</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>291697</t>
+          <t>349983</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8550,32 +8550,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>417640</t>
+          <t>359898</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>400161</t>
+          <t>347396</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>441495</t>
+          <t>369337</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8585,32 +8585,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>700291</t>
+          <t>700647</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>681561</t>
+          <t>685113</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>724894</t>
+          <t>715286</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>89,96%</t>
         </is>
       </c>
     </row>
@@ -8628,17 +8628,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8663,17 +8663,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8698,17 +8698,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8745,32 +8745,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10416</t>
+          <t>10895</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6392</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15611</t>
+          <t>16276</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8780,32 +8780,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>29659</t>
+          <t>30172</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15966</t>
+          <t>23856</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39597</t>
+          <t>36361</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8815,32 +8815,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>40075</t>
+          <t>41067</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27883</t>
+          <t>33658</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50579</t>
+          <t>50017</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -8858,32 +8858,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>168326</t>
+          <t>194770</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>163131</t>
+          <t>189389</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>172350</t>
+          <t>199034</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8893,32 +8893,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>229120</t>
+          <t>198746</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>219182</t>
+          <t>192557</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>242813</t>
+          <t>205062</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8928,32 +8928,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>397446</t>
+          <t>393515</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>386942</t>
+          <t>384565</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>409638</t>
+          <t>400924</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>92,26%</t>
         </is>
       </c>
     </row>
@@ -8971,17 +8971,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9006,17 +9006,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9041,17 +9041,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9088,17 +9088,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>40322</t>
+          <t>40466</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32633</t>
+          <t>31937</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50128</t>
+          <t>50106</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9123,32 +9123,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>64768</t>
+          <t>66783</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55377</t>
+          <t>56732</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>75629</t>
+          <t>77788</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9158,32 +9158,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>105090</t>
+          <t>107249</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>91954</t>
+          <t>94924</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>118691</t>
+          <t>121714</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,77%</t>
         </is>
       </c>
     </row>
@@ -9201,17 +9201,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>229314</t>
+          <t>230241</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>219508</t>
+          <t>220601</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237003</t>
+          <t>238770</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9236,32 +9236,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>192288</t>
+          <t>196967</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>181427</t>
+          <t>185962</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>201679</t>
+          <t>207018</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9271,32 +9271,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>421602</t>
+          <t>427208</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>408001</t>
+          <t>412743</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>434738</t>
+          <t>439533</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,24%</t>
         </is>
       </c>
     </row>
@@ -9314,17 +9314,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9349,17 +9349,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9384,17 +9384,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9431,32 +9431,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>51347</t>
+          <t>58429</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39585</t>
+          <t>45077</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67517</t>
+          <t>74229</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9466,32 +9466,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>135634</t>
+          <t>160689</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>65203</t>
+          <t>141370</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>186144</t>
+          <t>182768</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9501,32 +9501,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>186981</t>
+          <t>219118</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>118851</t>
+          <t>194092</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>227943</t>
+          <t>244147</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -9544,32 +9544,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>572932</t>
+          <t>661258</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>556762</t>
+          <t>645458</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>584694</t>
+          <t>674610</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9579,32 +9579,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>713631</t>
+          <t>611368</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>663121</t>
+          <t>589289</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>784062</t>
+          <t>630687</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9614,32 +9614,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1286563</t>
+          <t>1272626</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1245601</t>
+          <t>1247597</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1354693</t>
+          <t>1297652</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>86,99%</t>
         </is>
       </c>
     </row>
@@ -9657,17 +9657,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9692,17 +9692,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9727,17 +9727,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9774,32 +9774,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>30063</t>
+          <t>34222</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12314</t>
+          <t>25701</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45704</t>
+          <t>46174</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9809,32 +9809,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>89033</t>
+          <t>96313</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>74287</t>
+          <t>81403</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>105351</t>
+          <t>111329</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9844,32 +9844,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>119097</t>
+          <t>130535</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>76658</t>
+          <t>112593</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>150280</t>
+          <t>148640</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -9887,32 +9887,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>898657</t>
+          <t>763850</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>883016</t>
+          <t>751898</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>916406</t>
+          <t>772371</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9922,32 +9922,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>628698</t>
+          <t>735018</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>612380</t>
+          <t>720002</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>643444</t>
+          <t>749928</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9957,32 +9957,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1527355</t>
+          <t>1498868</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1496172</t>
+          <t>1480763</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1569794</t>
+          <t>1516810</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>93,09%</t>
         </is>
       </c>
     </row>
@@ -10000,17 +10000,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10035,17 +10035,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10070,17 +10070,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10117,32 +10117,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>230531</t>
+          <t>246701</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>178838</t>
+          <t>219051</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>263678</t>
+          <t>273162</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10152,32 +10152,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>517594</t>
+          <t>561666</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>413012</t>
+          <t>526629</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>567137</t>
+          <t>597294</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10187,32 +10187,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>748125</t>
+          <t>808367</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>650438</t>
+          <t>762491</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>818617</t>
+          <t>855960</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -10230,32 +10230,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3229286</t>
+          <t>3286061</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3196139</t>
+          <t>3259600</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3280979</t>
+          <t>3313711</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10265,32 +10265,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3194686</t>
+          <t>3175288</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3145143</t>
+          <t>3139660</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3299268</t>
+          <t>3210325</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10300,32 +10300,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6423972</t>
+          <t>6461349</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6353480</t>
+          <t>6413756</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6521659</t>
+          <t>6507225</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>89,51%</t>
         </is>
       </c>
     </row>
@@ -10343,17 +10343,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10378,17 +10378,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10413,17 +10413,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
